--- a/res/efficiency/pet-md/ollama-Lamarckvergence-14B-Q4_K_S/2025-02-19_13-30-54/stats_calculated-Lamarckvergence-14B-Q4_K_S.xlsx
+++ b/res/efficiency/pet-md/ollama-Lamarckvergence-14B-Q4_K_S/2025-02-19_13-30-54/stats_calculated-Lamarckvergence-14B-Q4_K_S.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>kWh (mean, std)</t>
   </si>
@@ -27,6 +27,12 @@
     <t>average power draw (mean, std)</t>
   </si>
   <si>
+    <t>output tokens (mean, std)</t>
+  </si>
+  <si>
+    <t>throughput (mean, std)</t>
+  </si>
+  <si>
     <t>(0.0429, 0.0004)</t>
   </si>
   <si>
@@ -34,6 +40,12 @@
   </si>
   <si>
     <t>(270.0657, 0.8104)</t>
+  </si>
+  <si>
+    <t>(12842.8, 229.1969)</t>
+  </si>
+  <si>
+    <t>(22.3809, 0.2285)</t>
   </si>
   <si>
     <t>Tag</t>
@@ -442,10 +454,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,16 +467,28 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -479,33 +503,33 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -513,16 +537,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -540,18 +564,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
